--- a/artfynd/A 15347-2023 artfynd.xlsx
+++ b/artfynd/A 15347-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2784,6 +2784,104 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127649237</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92032</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>67</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Sprickporing</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Diplomitoporus crustulinus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Långåker södra, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>759583</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7111017</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15347-2023 artfynd.xlsx
+++ b/artfynd/A 15347-2023 artfynd.xlsx
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127649230</v>
+        <v>127649098</v>
       </c>
       <c r="B3" t="n">
-        <v>57658</v>
+        <v>82859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,42 +791,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759567</v>
+        <v>759627</v>
       </c>
       <c r="R3" t="n">
-        <v>7111032</v>
+        <v>7110930</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127649098</v>
+        <v>127649230</v>
       </c>
       <c r="B4" t="n">
-        <v>82859</v>
+        <v>57658</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,34 +888,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759627</v>
+        <v>759567</v>
       </c>
       <c r="R4" t="n">
-        <v>7110930</v>
+        <v>7111032</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,32 +982,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127649235</v>
+        <v>127649238</v>
       </c>
       <c r="B5" t="n">
-        <v>58031</v>
+        <v>91348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760218</v>
+        <v>759621</v>
       </c>
       <c r="R5" t="n">
-        <v>7111239</v>
+        <v>7111009</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127649238</v>
+        <v>127649235</v>
       </c>
       <c r="B6" t="n">
-        <v>91348</v>
+        <v>58031</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>759621</v>
+        <v>760218</v>
       </c>
       <c r="R6" t="n">
-        <v>7111009</v>
+        <v>7111239</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1766,27 +1766,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127649076</v>
+        <v>127649052</v>
       </c>
       <c r="B13" t="n">
-        <v>91737</v>
+        <v>91295</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6040186</v>
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1801,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759556</v>
+        <v>759864</v>
       </c>
       <c r="R13" t="n">
-        <v>7111021</v>
+        <v>7111156</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1858,32 +1863,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127649052</v>
+        <v>127649076</v>
       </c>
       <c r="B14" t="n">
-        <v>91295</v>
+        <v>91737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759864</v>
+        <v>759556</v>
       </c>
       <c r="R14" t="n">
-        <v>7111156</v>
+        <v>7111021</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2063,7 @@
         <v>127649236</v>
       </c>
       <c r="B16" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>127649091</v>
       </c>
       <c r="B17" t="n">
-        <v>105484</v>
+        <v>105486</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2272,10 +2272,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127649231</v>
+        <v>127649226</v>
       </c>
       <c r="B18" t="n">
-        <v>57658</v>
+        <v>57661</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2283,16 +2283,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2305,7 +2305,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759621</v>
+        <v>760107</v>
       </c>
       <c r="R18" t="n">
-        <v>7110946</v>
+        <v>7111186</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2351,6 +2351,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Barkfläk på två granar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2377,7 +2382,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127649062</v>
+        <v>127649231</v>
       </c>
       <c r="B19" t="n">
         <v>57658</v>
@@ -2420,10 +2425,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759630</v>
+        <v>759621</v>
       </c>
       <c r="R19" t="n">
-        <v>7111000</v>
+        <v>7110946</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2482,10 +2487,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127649226</v>
+        <v>127649062</v>
       </c>
       <c r="B20" t="n">
-        <v>57661</v>
+        <v>57658</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2493,16 +2498,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2515,7 +2520,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2525,10 +2530,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>760107</v>
+        <v>759630</v>
       </c>
       <c r="R20" t="n">
-        <v>7111186</v>
+        <v>7111000</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2561,11 +2566,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Barkfläk på två granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 15347-2023 artfynd.xlsx
+++ b/artfynd/A 15347-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127649232</v>
       </c>
       <c r="B2" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127649098</v>
       </c>
       <c r="B3" t="n">
-        <v>82859</v>
+        <v>82861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127649230</v>
       </c>
       <c r="B4" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>127649238</v>
       </c>
       <c r="B5" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127649235</v>
       </c>
       <c r="B6" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>127649228</v>
       </c>
       <c r="B7" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>127649096</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>127649242</v>
       </c>
       <c r="B9" t="n">
-        <v>88733</v>
+        <v>88735</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>127649229</v>
       </c>
       <c r="B10" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>127649233</v>
       </c>
       <c r="B11" t="n">
-        <v>91784</v>
+        <v>91786</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>127649224</v>
       </c>
       <c r="B12" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>127649052</v>
       </c>
       <c r="B13" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>127649076</v>
       </c>
       <c r="B14" t="n">
-        <v>91737</v>
+        <v>91739</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>127649063</v>
       </c>
       <c r="B15" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>127649236</v>
       </c>
       <c r="B16" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>127649091</v>
       </c>
       <c r="B17" t="n">
-        <v>105486</v>
+        <v>105488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2272,10 +2272,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127649226</v>
+        <v>127649231</v>
       </c>
       <c r="B18" t="n">
-        <v>57661</v>
+        <v>57660</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2283,16 +2283,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2305,7 +2305,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>760107</v>
+        <v>759621</v>
       </c>
       <c r="R18" t="n">
-        <v>7111186</v>
+        <v>7110946</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2351,11 +2351,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Barkfläk på två granar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2382,10 +2377,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127649231</v>
+        <v>127649062</v>
       </c>
       <c r="B19" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,10 +2420,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759621</v>
+        <v>759630</v>
       </c>
       <c r="R19" t="n">
-        <v>7110946</v>
+        <v>7111000</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2487,10 +2482,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127649062</v>
+        <v>127649226</v>
       </c>
       <c r="B20" t="n">
-        <v>57658</v>
+        <v>57663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2498,16 +2493,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2520,7 +2515,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2530,10 +2525,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759630</v>
+        <v>760107</v>
       </c>
       <c r="R20" t="n">
-        <v>7111000</v>
+        <v>7111186</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2566,6 +2561,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Barkfläk på två granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2595,7 +2595,7 @@
         <v>127649240</v>
       </c>
       <c r="B21" t="n">
-        <v>82859</v>
+        <v>82861</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>127649099</v>
       </c>
       <c r="B22" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>127649237</v>
       </c>
       <c r="B23" t="n">
-        <v>92032</v>
+        <v>92034</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 15347-2023 artfynd.xlsx
+++ b/artfynd/A 15347-2023 artfynd.xlsx
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127649098</v>
+        <v>127649230</v>
       </c>
       <c r="B3" t="n">
-        <v>82861</v>
+        <v>57660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,34 +791,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759627</v>
+        <v>759567</v>
       </c>
       <c r="R3" t="n">
-        <v>7110930</v>
+        <v>7111032</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127649230</v>
+        <v>127649098</v>
       </c>
       <c r="B4" t="n">
-        <v>57660</v>
+        <v>82861</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,42 +896,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759567</v>
+        <v>759627</v>
       </c>
       <c r="R4" t="n">
-        <v>7111032</v>
+        <v>7110930</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127649242</v>
+        <v>127649229</v>
       </c>
       <c r="B9" t="n">
-        <v>88735</v>
+        <v>57660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,34 +1381,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759636</v>
+        <v>760179</v>
       </c>
       <c r="R9" t="n">
-        <v>7110932</v>
+        <v>7111211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,10 +1475,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127649229</v>
+        <v>127649242</v>
       </c>
       <c r="B10" t="n">
-        <v>57660</v>
+        <v>88735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,42 +1486,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760179</v>
+        <v>759636</v>
       </c>
       <c r="R10" t="n">
-        <v>7111211</v>
+        <v>7110932</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1766,32 +1766,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127649052</v>
+        <v>127649076</v>
       </c>
       <c r="B13" t="n">
-        <v>91297</v>
+        <v>91739</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1801,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759864</v>
+        <v>759556</v>
       </c>
       <c r="R13" t="n">
-        <v>7111156</v>
+        <v>7111021</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,27 +1858,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127649076</v>
+        <v>127649052</v>
       </c>
       <c r="B14" t="n">
-        <v>91739</v>
+        <v>91297</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6040186</v>
+        <v>5447</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759556</v>
+        <v>759864</v>
       </c>
       <c r="R14" t="n">
-        <v>7111021</v>
+        <v>7111156</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 15347-2023 artfynd.xlsx
+++ b/artfynd/A 15347-2023 artfynd.xlsx
@@ -2272,10 +2272,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127649231</v>
+        <v>127649226</v>
       </c>
       <c r="B18" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2283,16 +2283,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2305,7 +2305,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759621</v>
+        <v>760107</v>
       </c>
       <c r="R18" t="n">
-        <v>7110946</v>
+        <v>7111186</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2351,6 +2351,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Barkfläk på två granar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2377,7 +2382,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127649062</v>
+        <v>127649231</v>
       </c>
       <c r="B19" t="n">
         <v>57660</v>
@@ -2420,10 +2425,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759630</v>
+        <v>759621</v>
       </c>
       <c r="R19" t="n">
-        <v>7111000</v>
+        <v>7110946</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2482,10 +2487,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127649226</v>
+        <v>127649062</v>
       </c>
       <c r="B20" t="n">
-        <v>57663</v>
+        <v>57660</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2493,16 +2498,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2515,7 +2520,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2525,10 +2530,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>760107</v>
+        <v>759630</v>
       </c>
       <c r="R20" t="n">
-        <v>7111186</v>
+        <v>7111000</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2561,11 +2566,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Barkfläk på två granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 15347-2023 artfynd.xlsx
+++ b/artfynd/A 15347-2023 artfynd.xlsx
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127649230</v>
+        <v>127649098</v>
       </c>
       <c r="B3" t="n">
-        <v>57660</v>
+        <v>82861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,42 +791,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759567</v>
+        <v>759627</v>
       </c>
       <c r="R3" t="n">
-        <v>7111032</v>
+        <v>7110930</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127649098</v>
+        <v>127649230</v>
       </c>
       <c r="B4" t="n">
-        <v>82861</v>
+        <v>57660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,34 +888,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759627</v>
+        <v>759567</v>
       </c>
       <c r="R4" t="n">
-        <v>7110930</v>
+        <v>7111032</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127649229</v>
+        <v>127649242</v>
       </c>
       <c r="B9" t="n">
-        <v>57660</v>
+        <v>88735</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,42 +1381,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760179</v>
+        <v>759636</v>
       </c>
       <c r="R9" t="n">
-        <v>7111211</v>
+        <v>7110932</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,10 +1467,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127649242</v>
+        <v>127649229</v>
       </c>
       <c r="B10" t="n">
-        <v>88735</v>
+        <v>57660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,34 +1478,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759636</v>
+        <v>760179</v>
       </c>
       <c r="R10" t="n">
-        <v>7110932</v>
+        <v>7111211</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1766,27 +1766,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127649076</v>
+        <v>127649052</v>
       </c>
       <c r="B13" t="n">
-        <v>91739</v>
+        <v>91297</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6040186</v>
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1801,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759556</v>
+        <v>759864</v>
       </c>
       <c r="R13" t="n">
-        <v>7111021</v>
+        <v>7111156</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1858,32 +1863,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127649052</v>
+        <v>127649076</v>
       </c>
       <c r="B14" t="n">
-        <v>91297</v>
+        <v>91739</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759864</v>
+        <v>759556</v>
       </c>
       <c r="R14" t="n">
-        <v>7111156</v>
+        <v>7111021</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2272,10 +2272,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127649226</v>
+        <v>127649231</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>57660</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2283,16 +2283,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2305,7 +2305,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>760107</v>
+        <v>759621</v>
       </c>
       <c r="R18" t="n">
-        <v>7111186</v>
+        <v>7110946</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2351,11 +2351,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Barkfläk på två granar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2382,7 +2377,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127649231</v>
+        <v>127649062</v>
       </c>
       <c r="B19" t="n">
         <v>57660</v>
@@ -2425,10 +2420,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759621</v>
+        <v>759630</v>
       </c>
       <c r="R19" t="n">
-        <v>7110946</v>
+        <v>7111000</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2487,10 +2482,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127649062</v>
+        <v>127649226</v>
       </c>
       <c r="B20" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2498,16 +2493,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2520,7 +2515,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2530,10 +2525,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759630</v>
+        <v>760107</v>
       </c>
       <c r="R20" t="n">
-        <v>7111000</v>
+        <v>7111186</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2566,6 +2561,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Barkfläk på två granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2592,32 +2592,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127649240</v>
+        <v>127649099</v>
       </c>
       <c r="B21" t="n">
-        <v>82861</v>
+        <v>92622</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759773</v>
+        <v>759949</v>
       </c>
       <c r="R21" t="n">
-        <v>7111090</v>
+        <v>7111115</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2689,32 +2689,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127649099</v>
+        <v>127649240</v>
       </c>
       <c r="B22" t="n">
-        <v>92622</v>
+        <v>82861</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759949</v>
+        <v>759773</v>
       </c>
       <c r="R22" t="n">
-        <v>7111115</v>
+        <v>7111090</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 15347-2023 artfynd.xlsx
+++ b/artfynd/A 15347-2023 artfynd.xlsx
@@ -985,7 +985,7 @@
         <v>127649238</v>
       </c>
       <c r="B5" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>127649242</v>
       </c>
       <c r="B9" t="n">
-        <v>88735</v>
+        <v>88741</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>127649233</v>
       </c>
       <c r="B11" t="n">
-        <v>91786</v>
+        <v>91792</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>127649224</v>
       </c>
       <c r="B12" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>127649052</v>
       </c>
       <c r="B13" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>127649076</v>
       </c>
       <c r="B14" t="n">
-        <v>91739</v>
+        <v>91745</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>127649236</v>
       </c>
       <c r="B16" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>127649091</v>
       </c>
       <c r="B17" t="n">
-        <v>105488</v>
+        <v>105494</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,32 +2592,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127649099</v>
+        <v>127649240</v>
       </c>
       <c r="B21" t="n">
-        <v>92622</v>
+        <v>82861</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759949</v>
+        <v>759773</v>
       </c>
       <c r="R21" t="n">
-        <v>7111115</v>
+        <v>7111090</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2689,32 +2689,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127649240</v>
+        <v>127649099</v>
       </c>
       <c r="B22" t="n">
-        <v>82861</v>
+        <v>92628</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759773</v>
+        <v>759949</v>
       </c>
       <c r="R22" t="n">
-        <v>7111090</v>
+        <v>7111115</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2789,7 +2789,7 @@
         <v>127649237</v>
       </c>
       <c r="B23" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 15347-2023 artfynd.xlsx
+++ b/artfynd/A 15347-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127649232</v>
       </c>
       <c r="B2" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127649098</v>
+        <v>127649230</v>
       </c>
       <c r="B3" t="n">
-        <v>82861</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,34 +791,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759627</v>
+        <v>759567</v>
       </c>
       <c r="R3" t="n">
-        <v>7110930</v>
+        <v>7111032</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127649230</v>
+        <v>127649098</v>
       </c>
       <c r="B4" t="n">
-        <v>57660</v>
+        <v>82864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,42 +896,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759567</v>
+        <v>759627</v>
       </c>
       <c r="R4" t="n">
-        <v>7111032</v>
+        <v>7110930</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +985,7 @@
         <v>127649238</v>
       </c>
       <c r="B5" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127649235</v>
       </c>
       <c r="B6" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>127649228</v>
       </c>
       <c r="B7" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>127649096</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>127649242</v>
       </c>
       <c r="B9" t="n">
-        <v>88741</v>
+        <v>88744</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>127649229</v>
       </c>
       <c r="B10" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>127649233</v>
       </c>
       <c r="B11" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>127649224</v>
       </c>
       <c r="B12" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>127649052</v>
       </c>
       <c r="B13" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>127649076</v>
       </c>
       <c r="B14" t="n">
-        <v>91745</v>
+        <v>91748</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>127649063</v>
       </c>
       <c r="B15" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>127649236</v>
       </c>
       <c r="B16" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>127649091</v>
       </c>
       <c r="B17" t="n">
-        <v>105494</v>
+        <v>105497</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2272,10 +2272,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127649231</v>
+        <v>127649062</v>
       </c>
       <c r="B18" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759621</v>
+        <v>759630</v>
       </c>
       <c r="R18" t="n">
-        <v>7110946</v>
+        <v>7111000</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,10 +2377,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127649062</v>
+        <v>127649231</v>
       </c>
       <c r="B19" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759630</v>
+        <v>759621</v>
       </c>
       <c r="R19" t="n">
-        <v>7111000</v>
+        <v>7110946</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2485,7 +2485,7 @@
         <v>127649226</v>
       </c>
       <c r="B20" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2592,32 +2592,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127649240</v>
+        <v>127649099</v>
       </c>
       <c r="B21" t="n">
-        <v>82861</v>
+        <v>92631</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759773</v>
+        <v>759949</v>
       </c>
       <c r="R21" t="n">
-        <v>7111090</v>
+        <v>7111115</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2689,32 +2689,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127649099</v>
+        <v>127649240</v>
       </c>
       <c r="B22" t="n">
-        <v>92628</v>
+        <v>82864</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759949</v>
+        <v>759773</v>
       </c>
       <c r="R22" t="n">
-        <v>7111115</v>
+        <v>7111090</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2789,7 +2789,7 @@
         <v>127649237</v>
       </c>
       <c r="B23" t="n">
-        <v>92040</v>
+        <v>92043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 15347-2023 artfynd.xlsx
+++ b/artfynd/A 15347-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127649232</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127649230</v>
+        <v>127649098</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>82870</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,42 +791,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759567</v>
+        <v>759627</v>
       </c>
       <c r="R3" t="n">
-        <v>7111032</v>
+        <v>7110930</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127649098</v>
+        <v>127649230</v>
       </c>
       <c r="B4" t="n">
-        <v>82864</v>
+        <v>57669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,34 +888,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759627</v>
+        <v>759567</v>
       </c>
       <c r="R4" t="n">
-        <v>7110930</v>
+        <v>7111032</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +985,7 @@
         <v>127649238</v>
       </c>
       <c r="B5" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127649235</v>
       </c>
       <c r="B6" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>127649228</v>
       </c>
       <c r="B7" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>127649096</v>
       </c>
       <c r="B8" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>127649242</v>
       </c>
       <c r="B9" t="n">
-        <v>88744</v>
+        <v>88752</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>127649229</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>127649233</v>
       </c>
       <c r="B11" t="n">
-        <v>91795</v>
+        <v>91803</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>127649224</v>
       </c>
       <c r="B12" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,32 +1766,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127649052</v>
+        <v>127649076</v>
       </c>
       <c r="B13" t="n">
-        <v>91306</v>
+        <v>91756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1801,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759864</v>
+        <v>759556</v>
       </c>
       <c r="R13" t="n">
-        <v>7111156</v>
+        <v>7111021</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,27 +1858,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127649076</v>
+        <v>127649052</v>
       </c>
       <c r="B14" t="n">
-        <v>91748</v>
+        <v>91314</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6040186</v>
+        <v>5447</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759556</v>
+        <v>759864</v>
       </c>
       <c r="R14" t="n">
-        <v>7111021</v>
+        <v>7111156</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1958,7 +1958,7 @@
         <v>127649063</v>
       </c>
       <c r="B15" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>127649236</v>
       </c>
       <c r="B16" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>127649091</v>
       </c>
       <c r="B17" t="n">
-        <v>105497</v>
+        <v>105505</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2272,10 +2272,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127649062</v>
+        <v>127649231</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759630</v>
+        <v>759621</v>
       </c>
       <c r="R18" t="n">
-        <v>7111000</v>
+        <v>7110946</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,10 +2377,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127649231</v>
+        <v>127649226</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2388,16 +2388,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2410,7 +2410,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759621</v>
+        <v>760107</v>
       </c>
       <c r="R19" t="n">
-        <v>7110946</v>
+        <v>7111186</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2456,6 +2456,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Barkfläk på två granar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2482,10 +2487,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127649226</v>
+        <v>127649062</v>
       </c>
       <c r="B20" t="n">
-        <v>57666</v>
+        <v>57669</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2493,16 +2498,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2515,7 +2520,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2525,10 +2530,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>760107</v>
+        <v>759630</v>
       </c>
       <c r="R20" t="n">
-        <v>7111186</v>
+        <v>7111000</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2561,11 +2566,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Barkfläk på två granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2595,7 +2595,7 @@
         <v>127649099</v>
       </c>
       <c r="B21" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>127649240</v>
       </c>
       <c r="B22" t="n">
-        <v>82864</v>
+        <v>82870</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>127649237</v>
       </c>
       <c r="B23" t="n">
-        <v>92043</v>
+        <v>92051</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 15347-2023 artfynd.xlsx
+++ b/artfynd/A 15347-2023 artfynd.xlsx
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127649098</v>
+        <v>127649230</v>
       </c>
       <c r="B3" t="n">
-        <v>82870</v>
+        <v>57669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,34 +791,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759627</v>
+        <v>759567</v>
       </c>
       <c r="R3" t="n">
-        <v>7110930</v>
+        <v>7111032</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127649230</v>
+        <v>127649098</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>82870</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,42 +896,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759567</v>
+        <v>759627</v>
       </c>
       <c r="R4" t="n">
-        <v>7111032</v>
+        <v>7110930</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +985,7 @@
         <v>127649238</v>
       </c>
       <c r="B5" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127649242</v>
+        <v>127649229</v>
       </c>
       <c r="B9" t="n">
-        <v>88752</v>
+        <v>57669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,34 +1381,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759636</v>
+        <v>760179</v>
       </c>
       <c r="R9" t="n">
-        <v>7110932</v>
+        <v>7111211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,10 +1475,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127649229</v>
+        <v>127649242</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>88753</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,42 +1486,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760179</v>
+        <v>759636</v>
       </c>
       <c r="R10" t="n">
-        <v>7111211</v>
+        <v>7110932</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
         <v>127649233</v>
       </c>
       <c r="B11" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>127649224</v>
       </c>
       <c r="B12" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>127649076</v>
       </c>
       <c r="B13" t="n">
-        <v>91756</v>
+        <v>91757</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>127649052</v>
       </c>
       <c r="B14" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>127649236</v>
       </c>
       <c r="B16" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>127649091</v>
       </c>
       <c r="B17" t="n">
-        <v>105505</v>
+        <v>105506</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,10 +2377,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127649226</v>
+        <v>127649062</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>57669</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2388,16 +2388,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2410,7 +2410,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>760107</v>
+        <v>759630</v>
       </c>
       <c r="R19" t="n">
-        <v>7111186</v>
+        <v>7111000</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2456,11 +2456,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Barkfläk på två granar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2487,10 +2482,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127649062</v>
+        <v>127649226</v>
       </c>
       <c r="B20" t="n">
-        <v>57669</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2498,16 +2493,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2520,7 +2515,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2530,10 +2525,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759630</v>
+        <v>760107</v>
       </c>
       <c r="R20" t="n">
-        <v>7111000</v>
+        <v>7111186</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2566,6 +2561,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Barkfläk på två granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2595,7 +2595,7 @@
         <v>127649099</v>
       </c>
       <c r="B21" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>127649237</v>
       </c>
       <c r="B23" t="n">
-        <v>92051</v>
+        <v>92052</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 15347-2023 artfynd.xlsx
+++ b/artfynd/A 15347-2023 artfynd.xlsx
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127649230</v>
+        <v>127649098</v>
       </c>
       <c r="B3" t="n">
-        <v>57669</v>
+        <v>82870</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,42 +791,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759567</v>
+        <v>759627</v>
       </c>
       <c r="R3" t="n">
-        <v>7111032</v>
+        <v>7110930</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127649098</v>
+        <v>127649230</v>
       </c>
       <c r="B4" t="n">
-        <v>82870</v>
+        <v>57669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,34 +888,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759627</v>
+        <v>759567</v>
       </c>
       <c r="R4" t="n">
-        <v>7110930</v>
+        <v>7111032</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -2272,10 +2272,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127649231</v>
+        <v>127649226</v>
       </c>
       <c r="B18" t="n">
-        <v>57669</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2283,16 +2283,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2305,7 +2305,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759621</v>
+        <v>760107</v>
       </c>
       <c r="R18" t="n">
-        <v>7110946</v>
+        <v>7111186</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2351,6 +2351,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Barkfläk på två granar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2377,7 +2382,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127649062</v>
+        <v>127649231</v>
       </c>
       <c r="B19" t="n">
         <v>57669</v>
@@ -2420,10 +2425,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759630</v>
+        <v>759621</v>
       </c>
       <c r="R19" t="n">
-        <v>7111000</v>
+        <v>7110946</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2482,10 +2487,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127649226</v>
+        <v>127649062</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>57669</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2493,16 +2498,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2515,7 +2520,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2525,10 +2530,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>760107</v>
+        <v>759630</v>
       </c>
       <c r="R20" t="n">
-        <v>7111186</v>
+        <v>7111000</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2561,11 +2566,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Barkfläk på två granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2592,32 +2592,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127649099</v>
+        <v>127649240</v>
       </c>
       <c r="B21" t="n">
-        <v>92640</v>
+        <v>82870</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759949</v>
+        <v>759773</v>
       </c>
       <c r="R21" t="n">
-        <v>7111115</v>
+        <v>7111090</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2689,32 +2689,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127649240</v>
+        <v>127649099</v>
       </c>
       <c r="B22" t="n">
-        <v>82870</v>
+        <v>92640</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759773</v>
+        <v>759949</v>
       </c>
       <c r="R22" t="n">
-        <v>7111090</v>
+        <v>7111115</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 15347-2023 artfynd.xlsx
+++ b/artfynd/A 15347-2023 artfynd.xlsx
@@ -985,7 +985,7 @@
         <v>127649238</v>
       </c>
       <c r="B5" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127649229</v>
+        <v>127649242</v>
       </c>
       <c r="B9" t="n">
-        <v>57669</v>
+        <v>88754</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,42 +1381,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760179</v>
+        <v>759636</v>
       </c>
       <c r="R9" t="n">
-        <v>7111211</v>
+        <v>7110932</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,10 +1467,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127649242</v>
+        <v>127649229</v>
       </c>
       <c r="B10" t="n">
-        <v>88753</v>
+        <v>57669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,34 +1478,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759636</v>
+        <v>760179</v>
       </c>
       <c r="R10" t="n">
-        <v>7110932</v>
+        <v>7111211</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
         <v>127649233</v>
       </c>
       <c r="B11" t="n">
-        <v>91804</v>
+        <v>91805</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>127649224</v>
       </c>
       <c r="B12" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,27 +1766,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127649076</v>
+        <v>127649052</v>
       </c>
       <c r="B13" t="n">
-        <v>91757</v>
+        <v>91316</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6040186</v>
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1801,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759556</v>
+        <v>759864</v>
       </c>
       <c r="R13" t="n">
-        <v>7111021</v>
+        <v>7111156</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1858,32 +1863,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127649052</v>
+        <v>127649076</v>
       </c>
       <c r="B14" t="n">
-        <v>91315</v>
+        <v>91758</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759864</v>
+        <v>759556</v>
       </c>
       <c r="R14" t="n">
-        <v>7111156</v>
+        <v>7111021</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,42 +1955,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127649063</v>
+        <v>127649236</v>
       </c>
       <c r="B15" t="n">
-        <v>57669</v>
+        <v>98469</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -1998,10 +2002,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759741</v>
+        <v>759598</v>
       </c>
       <c r="R15" t="n">
-        <v>7111066</v>
+        <v>7111016</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,12 +2040,18 @@
           <t>2025-08-17</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gynnsam livsmiljö. Borde kunna finnas fler förekomster i närområdet.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2060,46 +2070,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127649236</v>
+        <v>127649063</v>
       </c>
       <c r="B16" t="n">
-        <v>98468</v>
+        <v>57669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2107,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759598</v>
+        <v>759741</v>
       </c>
       <c r="R16" t="n">
-        <v>7111016</v>
+        <v>7111066</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,18 +2151,12 @@
           <t>2025-08-17</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Gynnsam livsmiljö. Borde kunna finnas fler förekomster i närområdet.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>127649091</v>
       </c>
       <c r="B17" t="n">
-        <v>105506</v>
+        <v>105507</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2272,10 +2272,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127649226</v>
+        <v>127649231</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>57669</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2283,16 +2283,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2305,7 +2305,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>760107</v>
+        <v>759621</v>
       </c>
       <c r="R18" t="n">
-        <v>7111186</v>
+        <v>7110946</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2351,11 +2351,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Barkfläk på två granar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2382,10 +2377,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127649231</v>
+        <v>127649226</v>
       </c>
       <c r="B19" t="n">
-        <v>57669</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2393,16 +2388,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2415,7 +2410,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2425,10 +2420,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759621</v>
+        <v>760107</v>
       </c>
       <c r="R19" t="n">
-        <v>7110946</v>
+        <v>7111186</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2461,6 +2456,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Barkfläk på två granar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2592,32 +2592,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127649240</v>
+        <v>127649099</v>
       </c>
       <c r="B21" t="n">
-        <v>82870</v>
+        <v>92641</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759773</v>
+        <v>759949</v>
       </c>
       <c r="R21" t="n">
-        <v>7111090</v>
+        <v>7111115</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2689,32 +2689,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127649099</v>
+        <v>127649240</v>
       </c>
       <c r="B22" t="n">
-        <v>92640</v>
+        <v>82870</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759949</v>
+        <v>759773</v>
       </c>
       <c r="R22" t="n">
-        <v>7111115</v>
+        <v>7111090</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2789,7 +2789,7 @@
         <v>127649237</v>
       </c>
       <c r="B23" t="n">
-        <v>92052</v>
+        <v>92053</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 15347-2023 artfynd.xlsx
+++ b/artfynd/A 15347-2023 artfynd.xlsx
@@ -985,7 +985,7 @@
         <v>127649238</v>
       </c>
       <c r="B5" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127649242</v>
+        <v>127649229</v>
       </c>
       <c r="B9" t="n">
-        <v>88754</v>
+        <v>57669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,34 +1381,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759636</v>
+        <v>760179</v>
       </c>
       <c r="R9" t="n">
-        <v>7110932</v>
+        <v>7111211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,10 +1475,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127649229</v>
+        <v>127649242</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>88755</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,42 +1486,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760179</v>
+        <v>759636</v>
       </c>
       <c r="R10" t="n">
-        <v>7111211</v>
+        <v>7110932</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
         <v>127649233</v>
       </c>
       <c r="B11" t="n">
-        <v>91805</v>
+        <v>91806</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>127649224</v>
       </c>
       <c r="B12" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>127649052</v>
       </c>
       <c r="B13" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>127649076</v>
       </c>
       <c r="B14" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>127649236</v>
       </c>
       <c r="B15" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>127649091</v>
       </c>
       <c r="B17" t="n">
-        <v>105507</v>
+        <v>105508</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,10 +2377,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127649226</v>
+        <v>127649062</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>57669</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2388,16 +2388,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2410,7 +2410,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>760107</v>
+        <v>759630</v>
       </c>
       <c r="R19" t="n">
-        <v>7111186</v>
+        <v>7111000</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2456,11 +2456,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Barkfläk på två granar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2487,10 +2482,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127649062</v>
+        <v>127649226</v>
       </c>
       <c r="B20" t="n">
-        <v>57669</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2498,16 +2493,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2520,7 +2515,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2530,10 +2525,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759630</v>
+        <v>760107</v>
       </c>
       <c r="R20" t="n">
-        <v>7111000</v>
+        <v>7111186</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2566,6 +2561,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Barkfläk på två granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2595,7 +2595,7 @@
         <v>127649099</v>
       </c>
       <c r="B21" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>127649237</v>
       </c>
       <c r="B23" t="n">
-        <v>92053</v>
+        <v>92054</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 15347-2023 artfynd.xlsx
+++ b/artfynd/A 15347-2023 artfynd.xlsx
@@ -1766,32 +1766,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127649052</v>
+        <v>127649076</v>
       </c>
       <c r="B13" t="n">
-        <v>91317</v>
+        <v>91759</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1801,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759864</v>
+        <v>759556</v>
       </c>
       <c r="R13" t="n">
-        <v>7111156</v>
+        <v>7111021</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,27 +1858,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127649076</v>
+        <v>127649052</v>
       </c>
       <c r="B14" t="n">
-        <v>91759</v>
+        <v>91317</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6040186</v>
+        <v>5447</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759556</v>
+        <v>759864</v>
       </c>
       <c r="R14" t="n">
-        <v>7111021</v>
+        <v>7111156</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,46 +1955,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127649236</v>
+        <v>127649063</v>
       </c>
       <c r="B15" t="n">
-        <v>98470</v>
+        <v>57669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2002,10 +1998,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759598</v>
+        <v>759741</v>
       </c>
       <c r="R15" t="n">
-        <v>7111016</v>
+        <v>7111066</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2040,18 +2036,12 @@
           <t>2025-08-17</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Gynnsam livsmiljö. Borde kunna finnas fler förekomster i närområdet.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2070,42 +2060,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127649063</v>
+        <v>127649236</v>
       </c>
       <c r="B16" t="n">
-        <v>57669</v>
+        <v>98470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2113,10 +2107,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759741</v>
+        <v>759598</v>
       </c>
       <c r="R16" t="n">
-        <v>7111066</v>
+        <v>7111016</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2151,12 +2145,18 @@
           <t>2025-08-17</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Gynnsam livsmiljö. Borde kunna finnas fler förekomster i närområdet.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2592,32 +2592,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127649099</v>
+        <v>127649240</v>
       </c>
       <c r="B21" t="n">
-        <v>92642</v>
+        <v>82870</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759949</v>
+        <v>759773</v>
       </c>
       <c r="R21" t="n">
-        <v>7111115</v>
+        <v>7111090</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2689,32 +2689,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127649240</v>
+        <v>127649099</v>
       </c>
       <c r="B22" t="n">
-        <v>82870</v>
+        <v>92642</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759773</v>
+        <v>759949</v>
       </c>
       <c r="R22" t="n">
-        <v>7111090</v>
+        <v>7111115</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 15347-2023 artfynd.xlsx
+++ b/artfynd/A 15347-2023 artfynd.xlsx
@@ -982,32 +982,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127649238</v>
+        <v>127649235</v>
       </c>
       <c r="B5" t="n">
-        <v>91370</v>
+        <v>58042</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759621</v>
+        <v>760218</v>
       </c>
       <c r="R5" t="n">
-        <v>7111009</v>
+        <v>7111239</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127649235</v>
+        <v>127649238</v>
       </c>
       <c r="B6" t="n">
-        <v>58042</v>
+        <v>91370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>760218</v>
+        <v>759621</v>
       </c>
       <c r="R6" t="n">
-        <v>7111239</v>
+        <v>7111009</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127649229</v>
+        <v>127649242</v>
       </c>
       <c r="B9" t="n">
-        <v>57669</v>
+        <v>88755</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,42 +1381,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760179</v>
+        <v>759636</v>
       </c>
       <c r="R9" t="n">
-        <v>7111211</v>
+        <v>7110932</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,10 +1467,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127649242</v>
+        <v>127649229</v>
       </c>
       <c r="B10" t="n">
-        <v>88755</v>
+        <v>57669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,34 +1478,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759636</v>
+        <v>760179</v>
       </c>
       <c r="R10" t="n">
-        <v>7110932</v>
+        <v>7111211</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1955,42 +1955,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127649063</v>
+        <v>127649236</v>
       </c>
       <c r="B15" t="n">
-        <v>57669</v>
+        <v>98470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -1998,10 +2002,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759741</v>
+        <v>759598</v>
       </c>
       <c r="R15" t="n">
-        <v>7111066</v>
+        <v>7111016</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,12 +2040,18 @@
           <t>2025-08-17</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gynnsam livsmiljö. Borde kunna finnas fler förekomster i närområdet.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2060,46 +2070,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127649236</v>
+        <v>127649063</v>
       </c>
       <c r="B16" t="n">
-        <v>98470</v>
+        <v>57669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2107,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759598</v>
+        <v>759741</v>
       </c>
       <c r="R16" t="n">
-        <v>7111016</v>
+        <v>7111066</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,18 +2151,12 @@
           <t>2025-08-17</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Gynnsam livsmiljö. Borde kunna finnas fler förekomster i närområdet.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15347-2023 artfynd.xlsx
+++ b/artfynd/A 15347-2023 artfynd.xlsx
@@ -982,32 +982,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127649235</v>
+        <v>127649238</v>
       </c>
       <c r="B5" t="n">
-        <v>58042</v>
+        <v>91370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760218</v>
+        <v>759621</v>
       </c>
       <c r="R5" t="n">
-        <v>7111239</v>
+        <v>7111009</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127649238</v>
+        <v>127649235</v>
       </c>
       <c r="B6" t="n">
-        <v>91370</v>
+        <v>58042</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>759621</v>
+        <v>760218</v>
       </c>
       <c r="R6" t="n">
-        <v>7111009</v>
+        <v>7111239</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 15347-2023 artfynd.xlsx
+++ b/artfynd/A 15347-2023 artfynd.xlsx
@@ -982,32 +982,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127649238</v>
+        <v>127649235</v>
       </c>
       <c r="B5" t="n">
-        <v>91370</v>
+        <v>58042</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759621</v>
+        <v>760218</v>
       </c>
       <c r="R5" t="n">
-        <v>7111009</v>
+        <v>7111239</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127649235</v>
+        <v>127649238</v>
       </c>
       <c r="B6" t="n">
-        <v>58042</v>
+        <v>91370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>760218</v>
+        <v>759621</v>
       </c>
       <c r="R6" t="n">
-        <v>7111239</v>
+        <v>7111009</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127649242</v>
+        <v>127649229</v>
       </c>
       <c r="B9" t="n">
-        <v>88755</v>
+        <v>57669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,34 +1381,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759636</v>
+        <v>760179</v>
       </c>
       <c r="R9" t="n">
-        <v>7110932</v>
+        <v>7111211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,10 +1475,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127649229</v>
+        <v>127649242</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>88755</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,42 +1486,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760179</v>
+        <v>759636</v>
       </c>
       <c r="R10" t="n">
-        <v>7111211</v>
+        <v>7110932</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1766,27 +1766,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127649076</v>
+        <v>127649052</v>
       </c>
       <c r="B13" t="n">
-        <v>91759</v>
+        <v>91317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6040186</v>
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1801,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759556</v>
+        <v>759864</v>
       </c>
       <c r="R13" t="n">
-        <v>7111021</v>
+        <v>7111156</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1858,32 +1863,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127649052</v>
+        <v>127649076</v>
       </c>
       <c r="B14" t="n">
-        <v>91317</v>
+        <v>91759</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759864</v>
+        <v>759556</v>
       </c>
       <c r="R14" t="n">
-        <v>7111156</v>
+        <v>7111021</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 15347-2023 artfynd.xlsx
+++ b/artfynd/A 15347-2023 artfynd.xlsx
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127649229</v>
+        <v>127649242</v>
       </c>
       <c r="B9" t="n">
-        <v>57669</v>
+        <v>88755</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,42 +1381,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760179</v>
+        <v>759636</v>
       </c>
       <c r="R9" t="n">
-        <v>7111211</v>
+        <v>7110932</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,10 +1467,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127649242</v>
+        <v>127649229</v>
       </c>
       <c r="B10" t="n">
-        <v>88755</v>
+        <v>57669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,34 +1478,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759636</v>
+        <v>760179</v>
       </c>
       <c r="R10" t="n">
-        <v>7110932</v>
+        <v>7111211</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1766,32 +1766,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127649052</v>
+        <v>127649076</v>
       </c>
       <c r="B13" t="n">
-        <v>91317</v>
+        <v>91759</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1801,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759864</v>
+        <v>759556</v>
       </c>
       <c r="R13" t="n">
-        <v>7111156</v>
+        <v>7111021</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,27 +1858,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127649076</v>
+        <v>127649052</v>
       </c>
       <c r="B14" t="n">
-        <v>91759</v>
+        <v>91317</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6040186</v>
+        <v>5447</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759556</v>
+        <v>759864</v>
       </c>
       <c r="R14" t="n">
-        <v>7111021</v>
+        <v>7111156</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 15347-2023 artfynd.xlsx
+++ b/artfynd/A 15347-2023 artfynd.xlsx
@@ -1955,46 +1955,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127649236</v>
+        <v>127649063</v>
       </c>
       <c r="B15" t="n">
-        <v>98470</v>
+        <v>57669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2002,10 +1998,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759598</v>
+        <v>759741</v>
       </c>
       <c r="R15" t="n">
-        <v>7111016</v>
+        <v>7111066</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2040,18 +2036,12 @@
           <t>2025-08-17</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Gynnsam livsmiljö. Borde kunna finnas fler förekomster i närområdet.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2070,42 +2060,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127649063</v>
+        <v>127649236</v>
       </c>
       <c r="B16" t="n">
-        <v>57669</v>
+        <v>98470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2113,10 +2107,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759741</v>
+        <v>759598</v>
       </c>
       <c r="R16" t="n">
-        <v>7111066</v>
+        <v>7111016</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2151,12 +2145,18 @@
           <t>2025-08-17</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Gynnsam livsmiljö. Borde kunna finnas fler förekomster i närområdet.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15347-2023 artfynd.xlsx
+++ b/artfynd/A 15347-2023 artfynd.xlsx
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127649242</v>
+        <v>127649229</v>
       </c>
       <c r="B9" t="n">
-        <v>88755</v>
+        <v>57669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,34 +1381,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759636</v>
+        <v>760179</v>
       </c>
       <c r="R9" t="n">
-        <v>7110932</v>
+        <v>7111211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,10 +1475,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127649229</v>
+        <v>127649242</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>88755</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,42 +1486,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långåker södra, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760179</v>
+        <v>759636</v>
       </c>
       <c r="R10" t="n">
-        <v>7111211</v>
+        <v>7110932</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1766,27 +1766,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127649076</v>
+        <v>127649052</v>
       </c>
       <c r="B13" t="n">
-        <v>91759</v>
+        <v>91317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6040186</v>
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1801,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759556</v>
+        <v>759864</v>
       </c>
       <c r="R13" t="n">
-        <v>7111021</v>
+        <v>7111156</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1858,32 +1863,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127649052</v>
+        <v>127649076</v>
       </c>
       <c r="B14" t="n">
-        <v>91317</v>
+        <v>91759</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759864</v>
+        <v>759556</v>
       </c>
       <c r="R14" t="n">
-        <v>7111156</v>
+        <v>7111021</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,42 +1955,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127649063</v>
+        <v>127649236</v>
       </c>
       <c r="B15" t="n">
-        <v>57669</v>
+        <v>98470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -1998,10 +2002,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759741</v>
+        <v>759598</v>
       </c>
       <c r="R15" t="n">
-        <v>7111066</v>
+        <v>7111016</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,12 +2040,18 @@
           <t>2025-08-17</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gynnsam livsmiljö. Borde kunna finnas fler förekomster i närområdet.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2060,46 +2070,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127649236</v>
+        <v>127649063</v>
       </c>
       <c r="B16" t="n">
-        <v>98470</v>
+        <v>57669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2107,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759598</v>
+        <v>759741</v>
       </c>
       <c r="R16" t="n">
-        <v>7111016</v>
+        <v>7111066</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,18 +2151,12 @@
           <t>2025-08-17</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Gynnsam livsmiljö. Borde kunna finnas fler förekomster i närområdet.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15347-2023 artfynd.xlsx
+++ b/artfynd/A 15347-2023 artfynd.xlsx
@@ -2789,7 +2789,7 @@
         <v>127649237</v>
       </c>
       <c r="B23" t="n">
-        <v>92054</v>
+        <v>92062</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
